--- a/concessao_BID_capital_giro.xlsx
+++ b/concessao_BID_capital_giro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sicoob-my.sharepoint.com/personal/caua_paniagua_sicoob_com_br/Documents/Streamlit - Comercial de Crédito e Serviços/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_1F6C0890C0BCFE94BCE23D9FE6F854A268D2C6FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B33544A-E3E0-431A-B02A-A9F1737627AC}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_1F6C0890C0BCFE94BCE23D9FE6F854A268D2C6FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DEC4604-97D9-443E-8F66-4039A9F8A970}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="257">
   <si>
     <t>Ano Movimento</t>
   </si>
@@ -780,6 +780,21 @@
   </si>
   <si>
     <t>44805907</t>
+  </si>
+  <si>
+    <t>44805193</t>
+  </si>
+  <si>
+    <t>44886023</t>
+  </si>
+  <si>
+    <t>44803967</t>
+  </si>
+  <si>
+    <t>44903923</t>
+  </si>
+  <si>
+    <t>44885354</t>
   </si>
 </sst>
 </file>
@@ -819,18 +834,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1132,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q180"/>
+  <dimension ref="A1:Q185"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -10536,162 +10546,427 @@
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A178" s="7">
+      <c r="A178" s="1">
         <v>2026</v>
       </c>
-      <c r="B178" s="8">
+      <c r="B178" s="2">
         <v>46113</v>
       </c>
-      <c r="C178" s="7">
+      <c r="C178" s="1">
         <v>2009</v>
       </c>
-      <c r="D178" s="7">
+      <c r="D178" s="1">
         <v>4370</v>
       </c>
-      <c r="E178" s="6" t="s">
+      <c r="E178" t="s">
         <v>60</v>
       </c>
-      <c r="F178" s="6" t="s">
+      <c r="F178" t="s">
         <v>61</v>
       </c>
-      <c r="G178" s="7">
-        <v>-2</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I178" s="7">
+      <c r="G178" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H178" t="s">
+        <v>19</v>
+      </c>
+      <c r="I178" s="1">
         <v>145358</v>
       </c>
-      <c r="J178" s="6" t="s">
+      <c r="J178" t="s">
         <v>27</v>
       </c>
-      <c r="K178" s="6" t="s">
+      <c r="K178" t="s">
         <v>249</v>
       </c>
-      <c r="L178" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M178" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N178" s="9">
+      <c r="L178" t="s">
+        <v>22</v>
+      </c>
+      <c r="M178" t="s">
+        <v>23</v>
+      </c>
+      <c r="N178" s="5">
         <v>108800</v>
       </c>
-      <c r="O178" s="10">
+      <c r="O178" s="4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="P178" s="6" t="s">
+      <c r="P178" t="s">
         <v>29</v>
       </c>
-      <c r="Q178" s="7">
+      <c r="Q178" s="1">
         <v>261737042703</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A179" s="7">
+      <c r="A179" s="1">
         <v>2026</v>
       </c>
-      <c r="B179" s="8">
+      <c r="B179" s="2">
         <v>46111</v>
       </c>
-      <c r="C179" s="7">
+      <c r="C179" s="1">
         <v>1003</v>
       </c>
-      <c r="D179" s="7">
+      <c r="D179" s="1">
         <v>3172</v>
       </c>
-      <c r="E179" s="6" t="s">
+      <c r="E179" t="s">
         <v>17</v>
       </c>
-      <c r="F179" s="6" t="s">
+      <c r="F179" t="s">
         <v>18</v>
       </c>
-      <c r="G179" s="7">
-        <v>-2</v>
-      </c>
-      <c r="H179" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I179" s="7">
-        <v>145356</v>
-      </c>
-      <c r="J179" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K179" s="6" t="s">
+      <c r="G179" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H179" t="s">
+        <v>19</v>
+      </c>
+      <c r="I179" s="1">
+        <v>145356</v>
+      </c>
+      <c r="J179" t="s">
+        <v>20</v>
+      </c>
+      <c r="K179" t="s">
         <v>250</v>
       </c>
-      <c r="L179" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M179" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N179" s="9">
+      <c r="L179" t="s">
+        <v>22</v>
+      </c>
+      <c r="M179" t="s">
+        <v>23</v>
+      </c>
+      <c r="N179" s="5">
         <v>13920</v>
       </c>
-      <c r="O179" s="10">
+      <c r="O179" s="4">
         <v>1.17</v>
       </c>
-      <c r="P179" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q179" s="7">
+      <c r="P179" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q179" s="1">
         <v>266895102003</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A180" s="7">
+      <c r="A180" s="1">
         <v>2026</v>
       </c>
-      <c r="B180" s="8">
+      <c r="B180" s="2">
         <v>46113</v>
       </c>
-      <c r="C180" s="7">
+      <c r="C180" s="1">
         <v>2009</v>
       </c>
-      <c r="D180" s="7">
+      <c r="D180" s="1">
         <v>4370</v>
       </c>
-      <c r="E180" s="6" t="s">
+      <c r="E180" t="s">
         <v>60</v>
       </c>
-      <c r="F180" s="6" t="s">
+      <c r="F180" t="s">
         <v>61</v>
       </c>
-      <c r="G180" s="7">
-        <v>-2</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I180" s="7">
-        <v>145356</v>
-      </c>
-      <c r="J180" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K180" s="6" t="s">
+      <c r="G180" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H180" t="s">
+        <v>19</v>
+      </c>
+      <c r="I180" s="1">
+        <v>145356</v>
+      </c>
+      <c r="J180" t="s">
+        <v>20</v>
+      </c>
+      <c r="K180" t="s">
         <v>251</v>
       </c>
-      <c r="L180" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M180" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N180" s="9">
+      <c r="L180" t="s">
+        <v>22</v>
+      </c>
+      <c r="M180" t="s">
+        <v>23</v>
+      </c>
+      <c r="N180" s="5">
         <v>36000</v>
       </c>
-      <c r="O180" s="10">
+      <c r="O180" s="4">
         <v>1.2</v>
       </c>
-      <c r="P180" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q180" s="7">
+      <c r="P180" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q180" s="1">
         <v>261686412703</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B181" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C181" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D181" s="1">
+        <v>4370</v>
+      </c>
+      <c r="E181" t="s">
+        <v>60</v>
+      </c>
+      <c r="F181" t="s">
+        <v>61</v>
+      </c>
+      <c r="G181" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H181" t="s">
+        <v>19</v>
+      </c>
+      <c r="I181" s="1">
+        <v>145356</v>
+      </c>
+      <c r="J181" t="s">
+        <v>20</v>
+      </c>
+      <c r="K181" t="s">
+        <v>252</v>
+      </c>
+      <c r="L181" t="s">
+        <v>22</v>
+      </c>
+      <c r="M181" t="s">
+        <v>23</v>
+      </c>
+      <c r="N181" s="3">
+        <v>37437.599999999999</v>
+      </c>
+      <c r="O181" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="P181" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q181" s="1">
+        <v>261630572703</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B182" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C182" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D182" s="1">
+        <v>4370</v>
+      </c>
+      <c r="E182" t="s">
+        <v>60</v>
+      </c>
+      <c r="F182" t="s">
+        <v>61</v>
+      </c>
+      <c r="G182" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H182" t="s">
+        <v>19</v>
+      </c>
+      <c r="I182" s="1">
+        <v>145358</v>
+      </c>
+      <c r="J182" t="s">
+        <v>27</v>
+      </c>
+      <c r="K182" t="s">
+        <v>253</v>
+      </c>
+      <c r="L182" t="s">
+        <v>22</v>
+      </c>
+      <c r="M182" t="s">
+        <v>23</v>
+      </c>
+      <c r="N182" s="5">
+        <v>87600</v>
+      </c>
+      <c r="O182" s="4">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P182" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q182" s="1">
+        <v>263531453103</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B183" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C183" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D183" s="1">
+        <v>4370</v>
+      </c>
+      <c r="E183" t="s">
+        <v>60</v>
+      </c>
+      <c r="F183" t="s">
+        <v>61</v>
+      </c>
+      <c r="G183" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H183" t="s">
+        <v>19</v>
+      </c>
+      <c r="I183" s="1">
+        <v>145358</v>
+      </c>
+      <c r="J183" t="s">
+        <v>27</v>
+      </c>
+      <c r="K183" t="s">
+        <v>254</v>
+      </c>
+      <c r="L183" t="s">
+        <v>22</v>
+      </c>
+      <c r="M183" t="s">
+        <v>23</v>
+      </c>
+      <c r="N183" s="3">
+        <v>63444.51</v>
+      </c>
+      <c r="O183" s="4">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P183" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q183" s="1">
+        <v>261587932703</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B184" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C184" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D184" s="1">
+        <v>3172</v>
+      </c>
+      <c r="E184" t="s">
+        <v>17</v>
+      </c>
+      <c r="F184" t="s">
+        <v>18</v>
+      </c>
+      <c r="G184" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H184" t="s">
+        <v>19</v>
+      </c>
+      <c r="I184" s="1">
+        <v>145356</v>
+      </c>
+      <c r="J184" t="s">
+        <v>20</v>
+      </c>
+      <c r="K184" t="s">
+        <v>255</v>
+      </c>
+      <c r="L184" t="s">
+        <v>22</v>
+      </c>
+      <c r="M184" t="s">
+        <v>23</v>
+      </c>
+      <c r="N184" s="5">
+        <v>68620</v>
+      </c>
+      <c r="O184" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="P184" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q184" s="1">
+        <v>264106150104</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B185" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C185" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D185" s="1">
+        <v>4370</v>
+      </c>
+      <c r="E185" t="s">
+        <v>60</v>
+      </c>
+      <c r="F185" t="s">
+        <v>61</v>
+      </c>
+      <c r="G185" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H185" t="s">
+        <v>19</v>
+      </c>
+      <c r="I185" s="1">
+        <v>145356</v>
+      </c>
+      <c r="J185" t="s">
+        <v>20</v>
+      </c>
+      <c r="K185" t="s">
+        <v>256</v>
+      </c>
+      <c r="L185" t="s">
+        <v>22</v>
+      </c>
+      <c r="M185" t="s">
+        <v>23</v>
+      </c>
+      <c r="N185" s="5">
+        <v>52000</v>
+      </c>
+      <c r="O185" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="P185" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q185" s="1">
+        <v>263511553103</v>
       </c>
     </row>
   </sheetData>

--- a/concessao_BID_capital_giro.xlsx
+++ b/concessao_BID_capital_giro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sicoob-my.sharepoint.com/personal/caua_paniagua_sicoob_com_br/Documents/Streamlit - Comercial de Crédito e Serviços/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_1F6C0890C0BCFE94BCE23D9FE6F854A268D2C6FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DEC4604-97D9-443E-8F66-4039A9F8A970}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_1F6C0890C0BCFE94BCE23D9FE6F854A268D2C6FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CE1124C-66DE-4B8A-92EE-B13D93C63587}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,28 @@
     <sheet name="page" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">page!$A$1:$Q$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">page!$A$1:$Q$185</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <webPublishing codePage="1252"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="259">
   <si>
     <t>Ano Movimento</t>
   </si>
@@ -795,6 +808,12 @@
   </si>
   <si>
     <t>44885354</t>
+  </si>
+  <si>
+    <t>45082829</t>
+  </si>
+  <si>
+    <t>44971844</t>
   </si>
 </sst>
 </file>
@@ -834,13 +853,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1142,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q185"/>
+  <dimension ref="A1:Q187"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -10969,8 +10994,114 @@
         <v>263511553103</v>
       </c>
     </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A186" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B186" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C186" s="7">
+        <v>1003</v>
+      </c>
+      <c r="D186" s="7">
+        <v>3172</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G186" s="7">
+        <v>-2</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I186" s="7">
+        <v>145356</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K186" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="L186" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M186" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N186" s="9">
+        <v>39096</v>
+      </c>
+      <c r="O186" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="P186" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q186" s="7">
+        <v>261348811304</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A187" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B187" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C187" s="7">
+        <v>1005</v>
+      </c>
+      <c r="D187" s="7">
+        <v>3037</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G187" s="7">
+        <v>-2</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I187" s="7">
+        <v>145356</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K187" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="L187" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M187" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N187" s="11">
+        <v>1810032.8</v>
+      </c>
+      <c r="O187" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="P187" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q187" s="7">
+        <v>267267340704</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q165" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Q185" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 PÚBLICO&amp;1#_x000D_</oddHeader>
